--- a/data-input/people/people.xlsx
+++ b/data-input/people/people.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="16460"/>
+    <workbookView windowWidth="26860" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="TransportX学生信息" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TransportX学生信息!$A$1:$L$33</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="177">
   <si>
     <t>Name</t>
   </si>
@@ -65,454 +68,28 @@
     <t>other information</t>
   </si>
   <si>
-    <t>Linghui He</t>
-  </si>
-  <si>
-    <t>何凌晖</t>
-  </si>
-  <si>
-    <t>linghui_he.png</t>
-  </si>
-  <si>
-    <t>Ph.D</t>
-  </si>
-  <si>
-    <t>Graduate</t>
-  </si>
-  <si>
-    <t>Urban Transportation Emergency Management and Data Analytics</t>
-  </si>
-  <si>
-    <t>Eason_he@yeah.net</t>
-  </si>
-  <si>
-    <t>上海东方枢纽投资建设发展集团有限公司</t>
-  </si>
-  <si>
-    <t>guojun Zhu</t>
-  </si>
-  <si>
-    <t>朱国军</t>
-  </si>
-  <si>
-    <t>guojun_zhu.jpg</t>
+    <t>Yuhan Dong</t>
+  </si>
+  <si>
+    <t>董昱菡</t>
+  </si>
+  <si>
+    <t>yuhan_dong.jpg</t>
+  </si>
+  <si>
+    <t>Master</t>
   </si>
   <si>
     <t>Student</t>
-  </si>
-  <si>
-    <t>Dangerous Goods Transportation，Emergency Management，KAG and AGI</t>
-  </si>
-  <si>
-    <t>1910929@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Ranran Chen</t>
-  </si>
-  <si>
-    <t>陈冉冉</t>
-  </si>
-  <si>
-    <t>ranran_chen.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ph.D </t>
-  </si>
-  <si>
-    <t>Emergency Logistics</t>
-  </si>
-  <si>
-    <t>ranranchen@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Wenbin Zha</t>
-  </si>
-  <si>
-    <t>查文斌</t>
-  </si>
-  <si>
-    <t>weibin_zha.jpg</t>
-  </si>
-  <si>
-    <t>Travel Choice Modeling</t>
-  </si>
-  <si>
-    <t>wenbinzha@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Sanghuiyu Yan</t>
-  </si>
-  <si>
-    <t>阎桑慧宇</t>
-  </si>
-  <si>
-    <t>sanghuiyu_yan.jpg</t>
-  </si>
-  <si>
-    <t>Emergency transportation planning and system resilience</t>
-  </si>
-  <si>
-    <t>2111508@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Pengju Ren</t>
-  </si>
-  <si>
-    <t>任鹏举</t>
-  </si>
-  <si>
-    <t>pengju_ren.jpg</t>
-  </si>
-  <si>
-    <t>Decision Support for Transportation Policy-Making</t>
-  </si>
-  <si>
-    <t>2111509@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Rui Xu</t>
-  </si>
-  <si>
-    <t>许睿</t>
-  </si>
-  <si>
-    <t>rui_xu.jpg</t>
-  </si>
-  <si>
-    <t>logistics and operation management</t>
-  </si>
-  <si>
-    <t>Ray@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Yi Zhou</t>
-  </si>
-  <si>
-    <t>周漪</t>
-  </si>
-  <si>
-    <t>yi_zhou.jpg</t>
-  </si>
-  <si>
-    <t>Travel Behavior</t>
-  </si>
-  <si>
-    <t>703812208@qq.com</t>
-  </si>
-  <si>
-    <t>Xujun Zhou</t>
-  </si>
-  <si>
-    <t>周胥君</t>
-  </si>
-  <si>
-    <t>xujun_zhou.jpg</t>
-  </si>
-  <si>
-    <t>Shipping Data Mining and Modeling；Intelligent Planning；</t>
-  </si>
-  <si>
-    <t>2310851@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Yanjun Liu</t>
-  </si>
-  <si>
-    <t>刘彦君</t>
-  </si>
-  <si>
-    <t>yanjun_liu.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Mobility </t>
-  </si>
-  <si>
-    <t>liu666yanjun@163.con</t>
-  </si>
-  <si>
-    <t>Shuhang Chen</t>
-  </si>
-  <si>
-    <t>陈书航</t>
-  </si>
-  <si>
-    <t>shuhang_chen.jpg</t>
-  </si>
-  <si>
-    <t>Vessel dynamic information optimization and prediction with artificial intelligence algorithms</t>
-  </si>
-  <si>
-    <t>2480093@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Qiang Xia</t>
-  </si>
-  <si>
-    <t>夏强</t>
-  </si>
-  <si>
-    <t>qiang_xia.jpg</t>
-  </si>
-  <si>
-    <t>Human Mobility and LLMs</t>
-  </si>
-  <si>
-    <t>xiaqiang@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>https://ran-blog.vercel.app/</t>
-  </si>
-  <si>
-    <t>IBRAHIM ABDI MOHAMMED</t>
-  </si>
-  <si>
-    <t>Abdi</t>
-  </si>
-  <si>
-    <t>abdi.jpg</t>
-  </si>
-  <si>
-    <t>Transportation Accessibility &amp; ITS Model</t>
-  </si>
-  <si>
-    <t>2490043@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Zeal Li</t>
-  </si>
-  <si>
-    <t>zeal_li.jpg</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Traffic public opinion analysis based on machine learning</t>
-  </si>
-  <si>
-    <t>estel1016@163.com</t>
-  </si>
-  <si>
-    <t>Wayfair</t>
-  </si>
-  <si>
-    <t>Xinyuan Wang</t>
-  </si>
-  <si>
-    <t>王歆远</t>
-  </si>
-  <si>
-    <t>xinyuan_wang.jpg</t>
-  </si>
-  <si>
-    <t>Traffic Behavior and Multi-Agent simulation</t>
-  </si>
-  <si>
-    <t>faraway97@163.com</t>
-  </si>
-  <si>
-    <t>福建省高速公路集团科技创新研究院</t>
-  </si>
-  <si>
-    <t>Yimu Zhang</t>
-  </si>
-  <si>
-    <t>张懿木</t>
-  </si>
-  <si>
-    <t>yimu_zhang.png</t>
-  </si>
-  <si>
-    <t>Public Transportation Big Data Mining and Modeling</t>
-  </si>
-  <si>
-    <t>zymwork2022@163.com</t>
-  </si>
-  <si>
-    <t>郑州科技学院</t>
-  </si>
-  <si>
-    <t>Ziyue Xiong</t>
-  </si>
-  <si>
-    <t>熊子曰</t>
-  </si>
-  <si>
-    <t>ziyue_xiong.png</t>
-  </si>
-  <si>
-    <t>Ride-Hailing Operational Characteristics and Regulatory Policies</t>
-  </si>
-  <si>
-    <t>xzyolala@163.com</t>
-  </si>
-  <si>
-    <t>携程</t>
-  </si>
-  <si>
-    <t>Yuru Wu</t>
-  </si>
-  <si>
-    <t>yuru_wu.png</t>
-  </si>
-  <si>
-    <t>Transportation Planning</t>
-  </si>
-  <si>
-    <t>1377953378@qq.com</t>
-  </si>
-  <si>
-    <t>上海国际港务集团股份有限公司</t>
-  </si>
-  <si>
-    <t>Chenjie Xu</t>
-  </si>
-  <si>
-    <t>徐晨捷</t>
-  </si>
-  <si>
-    <t>chenjie_xu.png</t>
-  </si>
-  <si>
-    <t>Sustainable Transportation Planning</t>
-  </si>
-  <si>
-    <t>chenjie_xu@aliyun.com</t>
-  </si>
-  <si>
-    <t>上海市城乡建设和交通发展研究院</t>
-  </si>
-  <si>
-    <t>Rui Ma</t>
-  </si>
-  <si>
-    <t>马瑞</t>
-  </si>
-  <si>
-    <t>rui_ma.png</t>
-  </si>
-  <si>
-    <t>traffic resilience modeling</t>
-  </si>
-  <si>
-    <t>rm6968@nyu.edu</t>
-  </si>
-  <si>
-    <t>纽约大学</t>
-  </si>
-  <si>
-    <t>Yuhang Liu</t>
-  </si>
-  <si>
-    <t>刘宇航</t>
-  </si>
-  <si>
-    <t>yuhang_liu.jpg</t>
-  </si>
-  <si>
-    <t>Human mobility</t>
-  </si>
-  <si>
-    <t>2231311@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Ao Wang</t>
-  </si>
-  <si>
-    <t>王奥</t>
-  </si>
-  <si>
-    <t>ao_wang.jpg</t>
-  </si>
-  <si>
-    <t>Large Language Model, Blockchain</t>
-  </si>
-  <si>
-    <t>2331623@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>https://www.orville.wang/</t>
-  </si>
-  <si>
-    <t>Yilin Hao</t>
-  </si>
-  <si>
-    <t>郝一霖</t>
-  </si>
-  <si>
-    <t>yilin_hao.jpg</t>
-  </si>
-  <si>
-    <t>Travel behavior analysis, data pattern mining and city visitor identification, carbon neutrality</t>
-  </si>
-  <si>
-    <t>yilinh517@gmail.com</t>
-  </si>
-  <si>
-    <t>Xihan Yang</t>
-  </si>
-  <si>
-    <t>杨晰涵</t>
-  </si>
-  <si>
-    <t>xihan_yang.jpg</t>
-  </si>
-  <si>
-    <t>dmuyxh@163.com</t>
-  </si>
-  <si>
-    <t>Yizhe Li</t>
-  </si>
-  <si>
-    <t>李毅喆</t>
-  </si>
-  <si>
-    <t>yizhe_li.jpg</t>
-  </si>
-  <si>
-    <t>Knowledge graph, large model, evidence-based decision making</t>
-  </si>
-  <si>
-    <t>2051315@tongji.edu.cn</t>
-  </si>
-  <si>
-    <t>Yongsheng Lu</t>
-  </si>
-  <si>
-    <t>卢永晟</t>
-  </si>
-  <si>
-    <t>yongsheng_lu.jpg</t>
-  </si>
-  <si>
-    <t>Discovery and prediction of human mobile behavior patterns driven by LLMs</t>
-  </si>
-  <si>
-    <t>3243453195@qq.com</t>
-  </si>
-  <si>
-    <t>Zhiwei Huang</t>
-  </si>
-  <si>
-    <t>黄知微</t>
-  </si>
-  <si>
-    <t>zhiwei_huang.jpg</t>
-  </si>
-  <si>
-    <t>Yuhan Dong</t>
-  </si>
-  <si>
-    <t>董昱菡</t>
-  </si>
-  <si>
-    <t>yuhan_dong.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">女，21岁，贵州遵义人。本科毕业于同济大学交通学院，爱好手工，音乐，漫画。
 </t>
   </si>
   <si>
+    <t>Human Mobility and LLMs</t>
+  </si>
+  <si>
     <t>2131007889@qq.com</t>
   </si>
   <si>
@@ -532,6 +109,459 @@
   </si>
   <si>
     <t>396891501@qq.com</t>
+  </si>
+  <si>
+    <t>Yongsheng Lu</t>
+  </si>
+  <si>
+    <t>卢永晟</t>
+  </si>
+  <si>
+    <t>yongsheng_lu.jpg</t>
+  </si>
+  <si>
+    <t>Discovery and prediction of human mobile behavior patterns driven by LLMs</t>
+  </si>
+  <si>
+    <t>3243453195@qq.com</t>
+  </si>
+  <si>
+    <t>Zhiwei Huang</t>
+  </si>
+  <si>
+    <t>黄知微</t>
+  </si>
+  <si>
+    <t>zhiwei_huang.jpg</t>
+  </si>
+  <si>
+    <t>Shuhang Chen</t>
+  </si>
+  <si>
+    <t>陈书航</t>
+  </si>
+  <si>
+    <t>shuhang_chen.jpg</t>
+  </si>
+  <si>
+    <t>Ph.D</t>
+  </si>
+  <si>
+    <t>Vessel dynamic information optimization and prediction with artificial intelligence algorithms</t>
+  </si>
+  <si>
+    <t>2480093@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Qiang Xia</t>
+  </si>
+  <si>
+    <t>夏强</t>
+  </si>
+  <si>
+    <t>qiang_xia.jpg</t>
+  </si>
+  <si>
+    <t>xiaqiang@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>https://ran-blog.vercel.app/</t>
+  </si>
+  <si>
+    <t>IBRAHIM ABDI MOHAMMED</t>
+  </si>
+  <si>
+    <t>Abdi</t>
+  </si>
+  <si>
+    <t>abdi.jpg</t>
+  </si>
+  <si>
+    <t>Transportation Accessibility &amp; ITS Model</t>
+  </si>
+  <si>
+    <t>2490043@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Yizhe Li</t>
+  </si>
+  <si>
+    <t>李毅喆</t>
+  </si>
+  <si>
+    <t>yizhe_li.jpg</t>
+  </si>
+  <si>
+    <t>Knowledge graph, large model, evidence-based decision making</t>
+  </si>
+  <si>
+    <t>2051315@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Xujun Zhou</t>
+  </si>
+  <si>
+    <t>周胥君</t>
+  </si>
+  <si>
+    <t>xujun_zhou.jpg</t>
+  </si>
+  <si>
+    <t>Shipping Data Mining and Modeling；Intelligent Planning；</t>
+  </si>
+  <si>
+    <t>2310851@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Yanjun Liu</t>
+  </si>
+  <si>
+    <t>刘彦君</t>
+  </si>
+  <si>
+    <t>yanjun_liu.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Mobility </t>
+  </si>
+  <si>
+    <t>liu666yanjun@163.con</t>
+  </si>
+  <si>
+    <t>Ao Wang</t>
+  </si>
+  <si>
+    <t>王奥</t>
+  </si>
+  <si>
+    <t>ao_wang.jpg</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>Large Language Model, Blockchain</t>
+  </si>
+  <si>
+    <t>2331623@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>https://www.orville.wang/</t>
+  </si>
+  <si>
+    <t>Yilin Hao</t>
+  </si>
+  <si>
+    <t>郝一霖</t>
+  </si>
+  <si>
+    <t>yilin_hao.jpg</t>
+  </si>
+  <si>
+    <t>Travel behavior analysis, data pattern mining and city visitor identification, carbon neutrality</t>
+  </si>
+  <si>
+    <t>yilinh517@gmail.com</t>
+  </si>
+  <si>
+    <t>Xihan Yang</t>
+  </si>
+  <si>
+    <t>杨晰涵</t>
+  </si>
+  <si>
+    <t>xihan_yang.jpg</t>
+  </si>
+  <si>
+    <t>Transportation Planning</t>
+  </si>
+  <si>
+    <t>dmuyxh@163.com</t>
+  </si>
+  <si>
+    <t>Rui Xu</t>
+  </si>
+  <si>
+    <t>许睿</t>
+  </si>
+  <si>
+    <t>rui_xu.jpg</t>
+  </si>
+  <si>
+    <t>logistics and operation management</t>
+  </si>
+  <si>
+    <t>Ray@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Yi Zhou</t>
+  </si>
+  <si>
+    <t>周漪</t>
+  </si>
+  <si>
+    <t>yi_zhou.jpg</t>
+  </si>
+  <si>
+    <t>Travel Behavior</t>
+  </si>
+  <si>
+    <t>703812208@qq.com</t>
+  </si>
+  <si>
+    <t>Yuhang Liu</t>
+  </si>
+  <si>
+    <t>刘宇航</t>
+  </si>
+  <si>
+    <t>yuhang_liu.jpg</t>
+  </si>
+  <si>
+    <t>Human mobility</t>
+  </si>
+  <si>
+    <t>2231311@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Tao Xiang</t>
+  </si>
+  <si>
+    <t>向涛</t>
+  </si>
+  <si>
+    <t>tao_xiang.jpg</t>
+  </si>
+  <si>
+    <t>Zhenghang Hong</t>
+  </si>
+  <si>
+    <t>洪正航</t>
+  </si>
+  <si>
+    <t>zhenghang_hong.jpg</t>
+  </si>
+  <si>
+    <t>Sanghuiyu Yan</t>
+  </si>
+  <si>
+    <t>阎桑慧宇</t>
+  </si>
+  <si>
+    <t>sanghuiyu_yan.jpg</t>
+  </si>
+  <si>
+    <t>Emergency transportation planning and system resilience</t>
+  </si>
+  <si>
+    <t>2111508@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Pengju Ren</t>
+  </si>
+  <si>
+    <t>任鹏举</t>
+  </si>
+  <si>
+    <t>pengju_ren.jpg</t>
+  </si>
+  <si>
+    <t>Decision Support for Transportation Policy-Making</t>
+  </si>
+  <si>
+    <t>2111509@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Rui Ma</t>
+  </si>
+  <si>
+    <t>马瑞</t>
+  </si>
+  <si>
+    <t>rui_ma.png</t>
+  </si>
+  <si>
+    <t>traffic resilience modeling</t>
+  </si>
+  <si>
+    <t>rm6968@nyu.edu</t>
+  </si>
+  <si>
+    <t>纽约大学</t>
+  </si>
+  <si>
+    <t>Tian Gan</t>
+  </si>
+  <si>
+    <t>甘田</t>
+  </si>
+  <si>
+    <t>tian_gan.jpg</t>
+  </si>
+  <si>
+    <t>Ranran Chen</t>
+  </si>
+  <si>
+    <t>陈冉冉</t>
+  </si>
+  <si>
+    <t>ranran_chen.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ph.D </t>
+  </si>
+  <si>
+    <t>Emergency Logistics</t>
+  </si>
+  <si>
+    <t>ranranchen@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Wenbin Zha</t>
+  </si>
+  <si>
+    <t>查文斌</t>
+  </si>
+  <si>
+    <t>weibin_zha.jpg</t>
+  </si>
+  <si>
+    <t>Travel Choice Modeling</t>
+  </si>
+  <si>
+    <t>wenbinzha@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Yuru Wu</t>
+  </si>
+  <si>
+    <t>yuru_wu.png</t>
+  </si>
+  <si>
+    <t>1377953378@qq.com</t>
+  </si>
+  <si>
+    <t>上海国际港务集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Chenjie Xu</t>
+  </si>
+  <si>
+    <t>徐晨捷</t>
+  </si>
+  <si>
+    <t>chenjie_xu.png</t>
+  </si>
+  <si>
+    <t>Sustainable Transportation Planning</t>
+  </si>
+  <si>
+    <t>chenjie_xu@aliyun.com</t>
+  </si>
+  <si>
+    <t>上海市城乡建设和交通发展研究院</t>
+  </si>
+  <si>
+    <t>Linghui He</t>
+  </si>
+  <si>
+    <t>何凌晖</t>
+  </si>
+  <si>
+    <t>linghui_he.png</t>
+  </si>
+  <si>
+    <t>Urban Transportation Emergency Management and Data Analytics</t>
+  </si>
+  <si>
+    <t>Eason_he@yeah.net</t>
+  </si>
+  <si>
+    <t>上海东方枢纽投资建设发展集团有限公司</t>
+  </si>
+  <si>
+    <t>guojun Zhu</t>
+  </si>
+  <si>
+    <t>朱国军</t>
+  </si>
+  <si>
+    <t>guojun_zhu.jpg</t>
+  </si>
+  <si>
+    <t>Dangerous Goods Transportation，Emergency Management，KAG and AGI</t>
+  </si>
+  <si>
+    <t>1910929@tongji.edu.cn</t>
+  </si>
+  <si>
+    <t>Xinyuan Wang</t>
+  </si>
+  <si>
+    <t>王歆远</t>
+  </si>
+  <si>
+    <t>xinyuan_wang.jpg</t>
+  </si>
+  <si>
+    <t>Traffic Behavior and Multi-Agent simulation</t>
+  </si>
+  <si>
+    <t>faraway97@163.com</t>
+  </si>
+  <si>
+    <t>福建省高速公路集团科技创新研究院</t>
+  </si>
+  <si>
+    <t>Yimu Zhang</t>
+  </si>
+  <si>
+    <t>张懿木</t>
+  </si>
+  <si>
+    <t>yimu_zhang.png</t>
+  </si>
+  <si>
+    <t>Public Transportation Big Data Mining and Modeling</t>
+  </si>
+  <si>
+    <t>zymwork2022@163.com</t>
+  </si>
+  <si>
+    <t>郑州科技学院</t>
+  </si>
+  <si>
+    <t>Ziyue Xiong</t>
+  </si>
+  <si>
+    <t>熊子曰</t>
+  </si>
+  <si>
+    <t>ziyue_xiong.png</t>
+  </si>
+  <si>
+    <t>Ride-Hailing Operational Characteristics and Regulatory Policies</t>
+  </si>
+  <si>
+    <t>xzyolala@163.com</t>
+  </si>
+  <si>
+    <t>携程</t>
+  </si>
+  <si>
+    <t>Zeal Li</t>
+  </si>
+  <si>
+    <t>zeal_li.jpg</t>
+  </si>
+  <si>
+    <t>Traffic public opinion analysis based on machine learning</t>
+  </si>
+  <si>
+    <t>estel1016@163.com</t>
+  </si>
+  <si>
+    <t>Wayfair</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2"/>
   <cols>
     <col min="1" max="1" width="28.4230769230769" customWidth="1"/>
@@ -1508,7 +1538,7 @@
     <col min="12" max="12" width="20.5769230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" ht="14" customHeight="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,8 +1576,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="14" customHeight="1" spans="1:9">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
@@ -1559,25 +1589,24 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="F2">
+        <v>2026</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
       <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="14" customHeight="1" spans="1:9">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3" t="s">
@@ -1589,21 +1618,23 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <v>2026</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" ht="14" customHeight="1" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1614,31 +1645,31 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -1647,206 +1678,207 @@
         <v>16</v>
       </c>
       <c r="F5" s="1">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" ht="14" customHeight="1" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
+      <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1" spans="1:10">
+      <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
+      <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="B8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
+      <c r="C8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I8" t="s">
+      <c r="B9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
+      <c r="C9" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I9" t="s">
+      <c r="B10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1">
         <v>2023</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:9">
+      <c r="A11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I10" t="s">
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
+      <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1">
         <v>2023</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:10">
+      <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B12" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
+      <c r="C12" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F12" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
         <v>70</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" ht="14" customHeight="1" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
@@ -1860,10 +1892,10 @@
         <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F13" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
@@ -1872,223 +1904,194 @@
       <c r="I13" t="s">
         <v>76</v>
       </c>
-      <c r="J13" t="s">
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
+      <c r="B14" t="s">
         <v>78</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s">
         <v>81</v>
       </c>
-      <c r="I14" t="s">
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:9">
+      <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
+      <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
         <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" t="s">
         <v>86</v>
       </c>
-      <c r="I15" t="s">
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:9">
+      <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K15" t="s">
+      <c r="B16" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
+      <c r="C16" t="s">
         <v>89</v>
       </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="1">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1" spans="1:9">
+      <c r="A17" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I16" t="s">
+      <c r="B17" t="s">
         <v>93</v>
       </c>
-      <c r="K16" t="s">
+      <c r="C17" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F17" s="1">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1" spans="1:6">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
         <v>98</v>
       </c>
-      <c r="I17" t="s">
+      <c r="C18" t="s">
         <v>99</v>
       </c>
-      <c r="K17" t="s">
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1" spans="1:6">
+      <c r="A19" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
+      <c r="B19" t="s">
         <v>101</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C19" t="s">
         <v>102</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="1:9">
+      <c r="A20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1" t="s">
+      <c r="B20" t="s">
         <v>104</v>
       </c>
-      <c r="I18" t="s">
+      <c r="C20" t="s">
         <v>105</v>
       </c>
-      <c r="K18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I19" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" t="s">
-        <v>114</v>
-      </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="I20" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
@@ -2098,267 +2101,360 @@
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F22" s="1">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
+      </c>
+      <c r="K22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:6">
+      <c r="A23" t="s">
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I23" t="s">
-        <v>133</v>
-      </c>
-      <c r="J23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="F23">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="1">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F25" s="1">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B26" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F26" s="1">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>135</v>
+      </c>
+      <c r="K26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:11">
+      <c r="A28" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+      <c r="K28" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I29" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1" t="s">
+    <row r="30" ht="14" customHeight="1" spans="1:11">
+      <c r="A30" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>155</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
         <v>156</v>
       </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:9">
-      <c r="A29" t="s">
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B29" t="s">
+      <c r="I30" t="s">
         <v>158</v>
       </c>
-      <c r="C29" t="s">
+      <c r="K30" t="s">
         <v>159</v>
       </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29">
-        <v>2026</v>
-      </c>
-      <c r="G29" s="2" t="s">
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:11">
+      <c r="A31" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H29" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="B31" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
+      <c r="C31" t="s">
         <v>162</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C30" t="s">
+      <c r="I31" t="s">
         <v>164</v>
       </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30">
-        <v>2026</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="K31" t="s">
         <v>165</v>
       </c>
-      <c r="H30" t="s">
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:11">
+      <c r="A32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I30" t="s">
+      <c r="B32" t="s">
         <v>167</v>
       </c>
+      <c r="C32" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I32" t="s">
+        <v>170</v>
+      </c>
+      <c r="K32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:11">
+      <c r="A33" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I33" t="s">
+        <v>175</v>
+      </c>
+      <c r="K33" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L33" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:L33">
+      <sortCondition ref="F1" descending="1"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" display="1910929@tongji.edu.cn"/>
-    <hyperlink ref="I6" r:id="rId2" display="2111508@tongji.edu.cn"/>
-    <hyperlink ref="J13" r:id="rId3" display="https://ran-blog.vercel.app/"/>
-    <hyperlink ref="J23" r:id="rId4" display="https://www.orville.wang/"/>
-    <hyperlink ref="I30" r:id="rId5" display="396891501@qq.com"/>
+    <hyperlink ref="I29" r:id="rId1" display="1910929@tongji.edu.cn"/>
+    <hyperlink ref="I20" r:id="rId2" display="2111508@tongji.edu.cn"/>
+    <hyperlink ref="J7" r:id="rId3" display="https://ran-blog.vercel.app/"/>
+    <hyperlink ref="J12" r:id="rId4" display="https://www.orville.wang/"/>
+    <hyperlink ref="I3" r:id="rId5" display="396891501@qq.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
